--- a/backend/templates/采购订货单_模板.xlsx
+++ b/backend/templates/采购订货单_模板.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
   <si>
     <t xml:space="preserve"> 采 购 订 货 单 </t>
   </si>
@@ -52,6 +52,9 @@
     <t>产品型号</t>
   </si>
   <si>
+    <t>图片</t>
+  </si>
+  <si>
     <t>数量 (台)</t>
   </si>
   <si>
@@ -169,43 +172,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>四、 其他备注</t>
+  </si>
+  <si>
     <t>备注：</t>
-  </si>
-  <si>
-    <t>四、 质量要求与补充说明</t>
-  </si>
-  <si>
-    <t>1. 客户商标规范：</t>
-  </si>
-  <si>
-    <t>面贴、外壳铭牌及彩盒/外箱所印客户LOGO必须严格按照确认矢量图档执行，确保字迹清晰、色号准确、无重影毛刺；</t>
-  </si>
-  <si>
-    <t>2. 电压与电气规范：</t>
-  </si>
-  <si>
-    <t>3. 结构与密封要求：</t>
-  </si>
-  <si>
-    <t>整机结构密封严格，主板做加厚防潮三防漆喷涂，按键手感灵敏，传感器经四角偏差及线性度校准；</t>
-  </si>
-  <si>
-    <t>4. 电池安全规范：</t>
-  </si>
-  <si>
-    <t>必须使用带PTC保护板电池，出厂前每台需进行 100% 满负荷老化与连续通电测试 ≥ 24 小时；</t>
-  </si>
-  <si>
-    <t>5. 随箱配件清单：</t>
-  </si>
-  <si>
-    <t>每台包含主秤 1 台、不锈钢秤盘 1 块、标配电源线 1 条、中文说明书 1 份、合格证/保修卡 1 份、高透防尘罩 1 个；</t>
-  </si>
-  <si>
-    <t>6. 包装与唛头标识：</t>
-  </si>
-  <si>
-    <t>外箱清晰印制客户LOGO、产品型号、额定电压、净重/毛重、箱规尺寸及生产批次号，严禁混装。</t>
   </si>
 </sst>
 </file>
@@ -300,19 +270,10 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="7">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dashed">
-        <color rgb="FF94A3B8"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -344,43 +305,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFCBD5E1"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCBD5E1"/>
-      </right>
       <top style="thin">
         <color rgb="FFCBD5E1"/>
       </top>
@@ -430,73 +358,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,21 +707,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="17.875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="17.875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="33" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -824,586 +732,623 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="J7" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
         <v>1</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="10">
+      <c r="B8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8">
         <v>1000</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="10" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="G8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="B9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8">
         <v>500</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="F9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
         <v>3</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8">
         <v>800</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="F10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="12">
-        <f>SUM(C8:C12)</f>
-        <v>2300</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="15" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="20" t="s">
+      <c r="H18" s="13"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="18" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="5" t="s">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="H19" s="13"/>
+      <c r="I19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="18" t="s">
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="18" t="s">
+      <c r="H20" s="13"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="5" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="H21" s="13"/>
+      <c r="I21" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="22" t="s">
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23" t="s">
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-    </row>
-    <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" ht="34" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="A1:I1"/>
+  <mergeCells count="39">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:J15"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="A25:C29"/>
-    <mergeCell ref="D25:I29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="A25:D29"/>
+    <mergeCell ref="E25:J29"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:J31"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C19">
